--- a/TC/Apartment.xlsx
+++ b/TC/Apartment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\TC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19696FF-32DC-4E44-A809-CFAE05CD8B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC69ECA-0275-4D8D-84ED-81453EFF88FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="타이틀 화면" sheetId="1" r:id="rId1"/>
@@ -381,10 +381,6 @@
     <t>인게임 화면_5</t>
   </si>
   <si>
-    <t>W, A, S, D 키 중 하나를 
-누르고 있는 상태</t>
-  </si>
-  <si>
     <t>누르고 있던 이동 키에서 손을 뗀다.</t>
   </si>
   <si>
@@ -531,12 +527,129 @@
   <si>
     <t>게임 클리어 씬으로 이동한다.</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">W, A, S, D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누르고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -581,6 +694,20 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="5">
@@ -781,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -819,29 +946,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -858,26 +976,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1147,20 +1277,20 @@
     </row>
     <row r="2" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="1"/>
@@ -1176,18 +1306,18 @@
     </row>
     <row r="3" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="25"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="22"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
@@ -1203,32 +1333,32 @@
     </row>
     <row r="4" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="14" t="s">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="23" t="s">
         <v>8</v>
       </c>
       <c r="N4" s="3"/>
@@ -1246,8 +1376,8 @@
     </row>
     <row r="5" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1263,11 +1393,11 @@
       <c r="H5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="1"/>
@@ -1297,7 +1427,7 @@
       <c r="G6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="13" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -1332,19 +1462,19 @@
       <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="30" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="4" t="s">
@@ -1379,9 +1509,9 @@
       <c r="C8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="31"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="31"/>
+      <c r="F8" s="28"/>
       <c r="G8" s="8" t="s">
         <v>28</v>
       </c>
@@ -1420,9 +1550,9 @@
       <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="32"/>
-      <c r="F9" s="31"/>
+      <c r="F9" s="28"/>
       <c r="G9" s="8" t="s">
         <v>28</v>
       </c>
@@ -1461,9 +1591,9 @@
       <c r="C10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="32"/>
-      <c r="F10" s="31"/>
+      <c r="F10" s="28"/>
       <c r="G10" s="8" t="s">
         <v>28</v>
       </c>
@@ -1502,9 +1632,9 @@
       <c r="C11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="31"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="28"/>
+      <c r="F11" s="24"/>
       <c r="G11" s="8" t="s">
         <v>28</v>
       </c>
@@ -1543,9 +1673,9 @@
       <c r="C12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="31"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="30" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -1586,9 +1716,9 @@
       <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="28"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="8" t="s">
         <v>28</v>
       </c>
@@ -1627,21 +1757,21 @@
       <c r="C14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="28"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="30" t="s">
         <v>59</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="13" t="s">
         <v>61</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="13" t="s">
         <v>62</v>
       </c>
       <c r="K14" s="4" t="s">
@@ -1670,19 +1800,19 @@
       <c r="C15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="28"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="28"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="13" t="s">
         <v>65</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="30" t="s">
+      <c r="J15" s="13" t="s">
         <v>66</v>
       </c>
       <c r="K15" s="4" t="s">
@@ -1711,9 +1841,9 @@
       <c r="C16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="28"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="30" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="8" t="s">
@@ -1754,9 +1884,9 @@
       <c r="C17" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="31"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="31"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="8" t="s">
         <v>60</v>
       </c>
@@ -1795,9 +1925,9 @@
       <c r="C18" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="31"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="31"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="8" t="s">
         <v>60</v>
       </c>
@@ -1836,9 +1966,9 @@
       <c r="C19" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="32"/>
-      <c r="F19" s="28"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="8" t="s">
         <v>28</v>
       </c>
@@ -1877,9 +2007,9 @@
       <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="32"/>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="30" t="s">
         <v>59</v>
       </c>
       <c r="G20" s="4" t="s">
@@ -1920,9 +2050,9 @@
       <c r="C21" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="31"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="32"/>
-      <c r="F21" s="31"/>
+      <c r="F21" s="28"/>
       <c r="G21" s="4" t="s">
         <v>85</v>
       </c>
@@ -1961,9 +2091,9 @@
       <c r="C22" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="31"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="32"/>
-      <c r="F22" s="28"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="4" t="s">
         <v>85</v>
       </c>
@@ -2002,8 +2132,8 @@
       <c r="C23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="25"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="6" t="s">
         <v>19</v>
       </c>
@@ -2068,20 +2198,20 @@
     </row>
     <row r="25" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="27"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="16"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -28206,6 +28336,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="B25:M25"/>
     <mergeCell ref="F16:F19"/>
     <mergeCell ref="F20:F22"/>
@@ -28216,13 +28353,6 @@
     <mergeCell ref="F7:F11"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B2:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="3">
@@ -28290,20 +28420,20 @@
     </row>
     <row r="2" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="1"/>
@@ -28319,18 +28449,18 @@
     </row>
     <row r="3" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="25"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="22"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
@@ -28346,32 +28476,32 @@
     </row>
     <row r="4" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="14" t="s">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="23" t="s">
         <v>8</v>
       </c>
       <c r="N4" s="3"/>
@@ -28389,8 +28519,8 @@
     </row>
     <row r="5" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
@@ -28406,11 +28536,11 @@
       <c r="H5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="1"/>
@@ -28432,17 +28562,17 @@
       <c r="C6" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="29" t="s">
         <v>102</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="13" t="s">
         <v>104</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -28477,8 +28607,8 @@
       <c r="C7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8" t="s">
         <v>103</v>
@@ -28518,8 +28648,8 @@
       <c r="C8" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="7"/>
       <c r="G8" s="8" t="s">
         <v>103</v>
@@ -28559,8 +28689,8 @@
       <c r="C9" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="7"/>
       <c r="G9" s="8" t="s">
         <v>103</v>
@@ -28600,20 +28730,20 @@
       <c r="C10" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="8" t="s">
-        <v>116</v>
+      <c r="G10" s="33" t="s">
+        <v>164</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>21</v>
@@ -28639,22 +28769,22 @@
         <v>45</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8" t="s">
+      <c r="H11" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>21</v>
@@ -28680,22 +28810,22 @@
         <v>49</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8" t="s">
         <v>103</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>21</v>
@@ -28721,22 +28851,22 @@
         <v>53</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="7"/>
       <c r="G13" s="8" t="s">
         <v>103</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="30" t="s">
-        <v>128</v>
+      <c r="J13" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>21</v>
@@ -28762,22 +28892,22 @@
         <v>57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="7"/>
       <c r="G14" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="30" t="s">
-        <v>130</v>
+      <c r="H14" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="30" t="s">
-        <v>131</v>
+      <c r="J14" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>21</v>
@@ -28803,22 +28933,22 @@
         <v>63</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="7"/>
       <c r="G15" s="8" t="s">
         <v>103</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>21</v>
@@ -28844,26 +28974,26 @@
         <v>67</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="20" t="s">
+      <c r="F16" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="G16" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H16" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>21</v>
@@ -28889,22 +29019,22 @@
         <v>71</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>21</v>
@@ -28930,22 +29060,22 @@
         <v>75</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="8" t="s">
-        <v>145</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>21</v>
@@ -28971,22 +29101,22 @@
         <v>79</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="8" t="s">
         <v>145</v>
       </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="H19" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>21</v>
@@ -29012,26 +29142,26 @@
         <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="20" t="s">
+      <c r="F20" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>21</v>
@@ -29057,24 +29187,24 @@
         <v>88</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>21</v>
@@ -29100,24 +29230,24 @@
         <v>92</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="8" t="s">
-        <v>157</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>21</v>
@@ -29143,24 +29273,24 @@
         <v>94</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="24"/>
+      <c r="E23" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>21</v>
@@ -29182,20 +29312,20 @@
     </row>
     <row r="24" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="27"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="16"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
